--- a/Codelist Excel Files and Conversion Templates to XML/specificationDomain.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/specificationDomain.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes classifying which domain(s) of geotechnical/construction practice cite a registered standard in a diggs:SpecificationRegistry. Used for the value of the domain property of the diggs:SpecificationRegistryEntry object. A registry holds one canonical entry per real-world standard; a standard used by more than one domain (for example, ISO 22476-4, cited by both rigid inclusion design and in-situ testing) carries one domain code per domain rather than being registered a second time under a different identifier. This is what makes a single unified specification registry browsable and filterable by practice area without splitting it into several files.</t>
+          <t>Codes classifying the domain(s) of practice associated with a registered standard in a diggs:SpecificationRegistry. Used for the value of the domain property of the diggs:SpecificationRegistryEntry object. Values are drawn from two axes, and an entry normally carries at least one code from each: (1) the activity the standard governs - laboratory_testing, insitu_testing, observations, sampling, construction, design_codes or materials - which says what kind of measurement, observation, material or work the standard describes; and (2) the specialty area of practice that cites it - rigid_inclusions, deep_foundations, geophysics and similar - which is added whenever the standard is applicable to that specialty. A registry holds one canonical entry per real-world standard; a standard used by more than one domain (for example, ISO 22476-4, cited by both rigid inclusion design and in-situ testing) carries one domain code per domain rather than being registered a second time under a different identifier. This is what makes a single unified specification registry browsable and filterable by practice area without splitting it into several files.</t>
         </is>
       </c>
     </row>
@@ -1233,48 +1233,157 @@
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Observations</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Observation, description and classification practices whose result is a described or classified category rather than a measured quantity - soil and rock descriptions, borehole and stratigraphic logging, groundwater strike recording, corrosivity and aggressiveness classifications, and classification systems applied to measured test results.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>design_codes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Design codes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Design codes, standards of practice, recommendations, agency special provisions and research reports that set design requirements, design methods or acceptance criteria, as distinct from the test methods used to obtain the input values they consume.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
         <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2947,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Material property and supply specifications governing the constituents used in construction - concrete, grout, cement, reinforcement, geosynthetics, aggregates and engineered fill - including durability and exposure-class requirements.</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
         <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>geophysics</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Geophysics</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Geophysical methods: electrical resistivity, seismic, electromagnetic, thermal and other indirect measurements of ground properties, whether performed at the surface, in a borehole, or on a recovered sample.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F10" s="13" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
         <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>deep_foundations</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Deep foundations</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Deep foundation practice - driven, bored, augered, screw and micropile elements - and the design, execution, integrity and load-testing standards specific to them.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
@@ -1708,35 +1817,80 @@
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//diggs:SpecificationRegistryEntry/diggs:domain</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
         <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>design_codes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>//diggs:SpecificationRegistryEntry/diggs:domain</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
         <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>//diggs:SpecificationRegistryEntry/diggs:domain</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>geophysics</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:SpecificationRegistryEntry/diggs:domain</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>deep_foundations</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:SpecificationRegistryEntry/diggs:domain</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
